--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:08</t>
+    <t xml:space="preserve">2026-09-09 23:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:01</t>
+    <t xml:space="preserve">2026-09-17 13:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:59</t>
+    <t xml:space="preserve">2026-09-23 12:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:28</t>
+    <t xml:space="preserve">2026-10-02 13:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2019_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:51</t>
+    <t xml:space="preserve">2026-10-05 10:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -705,7 +705,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1499180.12</v>
+        <v>1499180.13</v>
       </c>
     </row>
     <row r="7">
@@ -739,7 +739,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1201880.62</v>
+        <v>1201880.63</v>
       </c>
     </row>
     <row r="9">
@@ -773,7 +773,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1143061.12</v>
+        <v>1143061.13</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>918286.62</v>
+        <v>918286.63</v>
       </c>
     </row>
     <row r="17">
@@ -926,7 +926,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>861146.12</v>
+        <v>861146.13</v>
       </c>
     </row>
     <row r="20">
@@ -943,7 +943,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>845097.62</v>
+        <v>845097.63</v>
       </c>
     </row>
     <row r="21">
@@ -994,7 +994,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>835797.12</v>
+        <v>835797.13</v>
       </c>
     </row>
     <row r="24">
@@ -1045,7 +1045,7 @@
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>833553.62</v>
+        <v>833553.63</v>
       </c>
     </row>
     <row r="27">
@@ -1147,7 +1147,7 @@
         <v>2019</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>751858.12</v>
+        <v>751858.13</v>
       </c>
     </row>
     <row r="33">
@@ -1249,7 +1249,7 @@
         <v>2019</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>702097.62</v>
+        <v>702097.63</v>
       </c>
     </row>
     <row r="39">
@@ -1487,7 +1487,7 @@
         <v>2019</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>616448.12</v>
+        <v>616448.13</v>
       </c>
     </row>
     <row r="53">
@@ -1504,7 +1504,7 @@
         <v>2019</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>585464.62</v>
+        <v>585464.63</v>
       </c>
     </row>
   </sheetData>
